--- a/artfynd/A 8838-2026 artfynd.xlsx
+++ b/artfynd/A 8838-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131420019</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131420017</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131420018</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>131420015</v>
       </c>
       <c r="B5" t="n">
-        <v>97261</v>
+        <v>97262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131420014</v>
       </c>
       <c r="B6" t="n">
-        <v>96251</v>
+        <v>96252</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8838-2026 artfynd.xlsx
+++ b/artfynd/A 8838-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131420019</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131420017</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131420018</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>131420015</v>
       </c>
       <c r="B5" t="n">
-        <v>97262</v>
+        <v>97263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131420014</v>
       </c>
       <c r="B6" t="n">
-        <v>96252</v>
+        <v>96253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8838-2026 artfynd.xlsx
+++ b/artfynd/A 8838-2026 artfynd.xlsx
@@ -1837,7 +1837,7 @@
         <v>131686421</v>
       </c>
       <c r="B13" t="n">
-        <v>96435</v>
+        <v>96438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>131686273</v>
       </c>
       <c r="B14" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Roger Gran</t>
+          <t>Roger Gran, Leif Appelgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 8838-2026 artfynd.xlsx
+++ b/artfynd/A 8838-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131420019</v>
+        <v>131420015</v>
       </c>
       <c r="B2" t="n">
-        <v>57911</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>360846</v>
+        <v>360880</v>
       </c>
       <c r="R2" t="n">
-        <v>6547463</v>
+        <v>6547448</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,11 +748,6 @@
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska hack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,17 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Roger Adolfsson, Leif Appelgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131420017</v>
+        <v>131542289</v>
       </c>
       <c r="B3" t="n">
-        <v>57911</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>S. Länsmanstjärnet, Dls</t>
+          <t>Länsmanstjärnet, S om, V om Skällebyn, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>360924</v>
+        <v>360910</v>
       </c>
       <c r="R3" t="n">
-        <v>6547356</v>
+        <v>6547364</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,11 +845,6 @@
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>gamla hack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -863,48 +853,58 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Roger Adolfsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131420018</v>
+        <v>131420014</v>
       </c>
       <c r="B4" t="n">
-        <v>57911</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>360876</v>
+        <v>360866</v>
       </c>
       <c r="R4" t="n">
-        <v>6547441</v>
+        <v>6547446</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,11 +952,6 @@
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska hack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -974,52 +969,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Leif Appelgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131420015</v>
+        <v>131686421</v>
       </c>
       <c r="B5" t="n">
-        <v>97294</v>
+        <v>96533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>S. Länsmanstjärnet, Dls</t>
+          <t>Länsmanstjärnet, S om, V om Skällebyn, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>360880</v>
+        <v>360779</v>
       </c>
       <c r="R5" t="n">
-        <v>6547448</v>
+        <v>6547188</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,12 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1062,64 +1057,85 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Sumpskog med grov klibbal</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Roger Adolfsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131542290</v>
+        <v>131673576</v>
       </c>
       <c r="B6" t="n">
-        <v>75382</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Länsmanstjärnet, S om, V om Skällebyn, Dls</t>
+          <t>Söder Länsmanstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>360966</v>
+        <v>361084</v>
       </c>
       <c r="R6" t="n">
-        <v>6547248</v>
+        <v>6547325</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1143,12 +1159,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På stammen av en gammal tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1157,83 +1178,64 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gammal barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Barken på gammal gran. # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran, Leif Appelgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131420014</v>
+        <v>131542290</v>
       </c>
       <c r="B7" t="n">
-        <v>96284</v>
+        <v>75428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>S. Länsmanstjärnet, Dls</t>
+          <t>Länsmanstjärnet, S om, V om Skällebyn, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>360866</v>
+        <v>360966</v>
       </c>
       <c r="R7" t="n">
-        <v>6547446</v>
+        <v>6547248</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,25 +1279,45 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Barken på gammal gran. # Picea abies</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Roger Adolfsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131542289</v>
+        <v>131686273</v>
       </c>
       <c r="B8" t="n">
-        <v>97294</v>
+        <v>75468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1325,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>360910</v>
+        <v>361095</v>
       </c>
       <c r="R8" t="n">
-        <v>6547364</v>
+        <v>6547317</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,12 +1379,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,7 +1403,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På granlåga.</t>
+          <t>Barken på gammal gran.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1392,17 +1414,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Leif Appelgren, Roger Gran</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131673587</v>
+        <v>131420017</v>
       </c>
       <c r="B9" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,46 +1432,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söder Länsmanstjärnet, Dls</t>
+          <t>S. Länsmanstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>361178</v>
+        <v>360924</v>
       </c>
       <c r="R9" t="n">
-        <v>6547307</v>
+        <v>6547356</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1473,12 +1486,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>gamla hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1487,29 +1505,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Gran, Leif Appelgren</t>
+          <t>Roger Adolfsson, Leif Appelgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131673589</v>
+        <v>131420018</v>
       </c>
       <c r="B10" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,46 +1534,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Söder Länsmanstjärnet, Dls</t>
+          <t>S. Länsmanstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>361178</v>
+        <v>360876</v>
       </c>
       <c r="R10" t="n">
-        <v>6547307</v>
+        <v>6547441</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1580,12 +1588,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,78 +1607,66 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Gran, Leif Appelgren</t>
+          <t>Roger Adolfsson, Leif Appelgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131673576</v>
+        <v>131420019</v>
       </c>
       <c r="B11" t="n">
-        <v>79315</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söder Länsmanstjärnet, Dls</t>
+          <t>S. Länsmanstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>361084</v>
+        <v>360846</v>
       </c>
       <c r="R11" t="n">
-        <v>6547325</v>
+        <v>6547463</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1689,17 +1690,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På stammen av en gammal tall</t>
+          <t>färska hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,29 +1709,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Roger Gran, Leif Appelgren</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131673592</v>
+        <v>131673589</v>
       </c>
       <c r="B12" t="n">
-        <v>5199</v>
+        <v>4776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131686421</v>
+        <v>131673587</v>
       </c>
       <c r="B13" t="n">
-        <v>96438</v>
+        <v>5181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1845,37 +1845,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Länsmanstjärnet, S om, V om Skällebyn, Dls</t>
+          <t>Söder Länsmanstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>360779</v>
+        <v>361178</v>
       </c>
       <c r="R13" t="n">
-        <v>6547188</v>
+        <v>6547307</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1913,38 +1922,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Sumpskog med grov klibbal</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran, Leif Appelgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131686273</v>
+        <v>131673592</v>
       </c>
       <c r="B14" t="n">
-        <v>75423</v>
+        <v>5201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,37 +1952,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Länsmanstjärnet, S om, V om Skällebyn, Dls</t>
+          <t>Söder Länsmanstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>361095</v>
+        <v>361178</v>
       </c>
       <c r="R14" t="n">
-        <v>6547317</v>
+        <v>6547307</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2020,23 +2029,14 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Gammal barrskog</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Barken på gammal gran.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
